--- a/tests/reference_data/test_scenario.xlsx
+++ b/tests/reference_data/test_scenario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBC8DC8-F20F-497E-841A-2EB6E3A862A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C3D377-DD1F-46F4-B60F-58906398B560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-25635" yWindow="2265" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="5" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
